--- a/dataset/construct/dataset_splits/data_size/20_percent/tum/fold2.xlsx
+++ b/dataset/construct/dataset_splits/data_size/20_percent/tum/fold2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN11"/>
+  <dimension ref="A1:AK11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2246</v>
+        <v>474</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,77 +625,79 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>76.92898734377771</v>
+        <v>78.2075977577509</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>27.6816608996539</v>
       </c>
       <c r="E2" t="n">
-        <v>22.7244034844085</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>49</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>187</v>
+      </c>
+      <c r="I2" t="n">
+        <v>222</v>
+      </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="K2" t="n">
-        <v>225.3</v>
+        <v>630</v>
       </c>
       <c r="L2" t="n">
-        <v>178.6</v>
+        <v>11</v>
       </c>
       <c r="M2" t="n">
-        <v>267.7</v>
+        <v>25</v>
       </c>
       <c r="N2" t="n">
-        <v>671.6</v>
+        <v>23</v>
       </c>
       <c r="O2" t="n">
-        <v>25.6</v>
+        <v>59</v>
       </c>
       <c r="P2" t="n">
-        <v>90.3</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>211.9</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>54.7</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>63.1</v>
+        <v>26.8</v>
       </c>
       <c r="V2" t="n">
-        <v>117.8</v>
+        <v>0.21</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>26.7379679144385</v>
       </c>
       <c r="X2" t="n">
-        <v>24.5</v>
+        <v>26.4345313179585</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.298611111111111</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>24.6052966641202</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>23.9831715115263</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -722,39 +709,28 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>114</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>168</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>983</v>
+        <v>2359</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -762,79 +738,79 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>74.1668630694349</v>
+        <v>84.26097786270191</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>24.2214532871972</v>
       </c>
       <c r="E3" t="n">
-        <v>25.4580659041199</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>60</v>
+        <v>376.3</v>
       </c>
       <c r="I3" t="n">
-        <v>1060</v>
+        <v>779</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>320.1</v>
       </c>
       <c r="K3" t="n">
-        <v>993</v>
+        <v>1475.4</v>
       </c>
       <c r="L3" t="n">
-        <v>491</v>
+        <v>140.7</v>
       </c>
       <c r="M3" t="n">
-        <v>960</v>
+        <v>42.8</v>
       </c>
       <c r="N3" t="n">
-        <v>2444</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>227</v>
+        <v>272.6</v>
       </c>
       <c r="P3" t="n">
-        <v>100</v>
+        <v>34.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>370</v>
+        <v>3.1</v>
       </c>
       <c r="S3" t="n">
-        <v>151</v>
+        <v>37.5</v>
       </c>
       <c r="T3" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>17</v>
+        <v>24.35</v>
       </c>
       <c r="V3" t="n">
-        <v>206</v>
+        <v>0.31</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>24.5734657499363</v>
       </c>
       <c r="X3" t="n">
-        <v>24.35</v>
+        <v>23.6975361509812</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.169172932330827</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.8731856378915</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.6921643870788</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -843,7 +819,7 @@
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -858,27 +834,18 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
         <v>136</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>118</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>501</v>
+        <v>365</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -886,40 +853,40 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>80.7024477463432</v>
+        <v>86.5307742033615</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>30.4878048780487</v>
       </c>
       <c r="E4" t="n">
-        <v>24.7675659198292</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>60</v>
+        <v>145</v>
       </c>
       <c r="I4" t="n">
-        <v>983</v>
+        <v>62</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="K4" t="n">
-        <v>37</v>
+        <v>274</v>
       </c>
       <c r="L4" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -937,34 +904,34 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>22.25</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>22.2816399286988</v>
       </c>
       <c r="X4" t="n">
-        <v>19.8</v>
+        <v>21.4950646217447</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.191780821917808</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>20.0534759358289</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>19.9279552640389</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -973,36 +940,25 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>132</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>959</v>
+        <v>936</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1010,79 +966,79 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>75.6452314814815</v>
+        <v>91.0289564795802</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>23.1111111111111</v>
       </c>
       <c r="E5" t="n">
-        <v>19.9510204081632</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>60</v>
+        <v>396</v>
       </c>
       <c r="I5" t="n">
-        <v>5050</v>
+        <v>148</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>307</v>
       </c>
       <c r="K5" t="n">
-        <v>281</v>
+        <v>851</v>
       </c>
       <c r="L5" t="n">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="M5" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="N5" t="n">
-        <v>394</v>
+        <v>66</v>
       </c>
       <c r="O5" t="n">
-        <v>10</v>
+        <v>112</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>20.05</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>20.3717850776674</v>
       </c>
       <c r="X5" t="n">
-        <v>22.4</v>
+        <v>19.8319163664306</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.283524904214559</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>23.2365673542144</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.6203056614775</v>
+        <v>1</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1097,7 +1053,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1109,22 +1065,15 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>126</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
+        <v>178</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>516</v>
+        <v>1109</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1132,121 +1081,114 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>82.09534185109131</v>
+        <v>79.1909800174918</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>28.3937263385613</v>
       </c>
       <c r="E6" t="n">
-        <v>29.0256076388888</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>50</v>
+        <v>187</v>
       </c>
       <c r="I6" t="n">
-        <v>2800</v>
+        <v>173</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>158</v>
       </c>
       <c r="K6" t="n">
-        <v>797</v>
+        <v>518</v>
       </c>
       <c r="L6" t="n">
-        <v>410</v>
+        <v>24</v>
       </c>
       <c r="M6" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1631</v>
+        <v>14</v>
       </c>
       <c r="O6" t="n">
-        <v>133</v>
+        <v>38</v>
       </c>
       <c r="P6" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>247</v>
+        <v>33</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="T6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="V6" t="n">
-        <v>9</v>
+        <v>0.21</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>30.2393684746626</v>
       </c>
       <c r="X6" t="n">
-        <v>25</v>
+        <v>29.7425256555005</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.257839721254355</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>25.1464222052457</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>24.6143810163112</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>194</v>
-      </c>
-      <c r="AN6" t="inlineStr"/>
+        <v>180</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2359</v>
+        <v>2121</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1254,79 +1196,79 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>84.26097786270191</v>
+        <v>82.77180653788631</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>23.0300453514739</v>
       </c>
       <c r="E7" t="n">
-        <v>24.2214532871972</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>4510</v>
+        <v>56.6</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>67.3</v>
       </c>
       <c r="K7" t="n">
-        <v>376.3</v>
+        <v>123.9</v>
       </c>
       <c r="L7" t="n">
-        <v>779</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>320.1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1475.4</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>140.7</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>42.8</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>89.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>272.6</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>34.4</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>3.1</v>
+        <v>22.8</v>
       </c>
       <c r="V7" t="n">
-        <v>37.5</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>22.5681181563535</v>
       </c>
       <c r="X7" t="n">
-        <v>24.35</v>
+        <v>22.1942730679895</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.314878892733564</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>24.5734657499363</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>23.6975361509812</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1344,7 +1286,7 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
@@ -1353,24 +1295,13 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>134</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>136</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="AK7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>347</v>
+        <v>635</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1378,77 +1309,79 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>84.5302151304282</v>
+        <v>79.51356757167849</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>21.09375</v>
       </c>
       <c r="E8" t="n">
-        <v>27.0416441319632</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>45</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>523</v>
+      </c>
+      <c r="I8" t="n">
+        <v>178</v>
+      </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>279</v>
       </c>
       <c r="K8" t="n">
-        <v>346</v>
+        <v>980</v>
       </c>
       <c r="L8" t="n">
-        <v>162.8</v>
+        <v>96</v>
       </c>
       <c r="M8" t="n">
-        <v>134.3</v>
+        <v>65</v>
       </c>
       <c r="N8" t="n">
-        <v>643.1</v>
+        <v>58</v>
       </c>
       <c r="O8" t="n">
-        <v>39.2</v>
+        <v>219</v>
       </c>
       <c r="P8" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>48.8</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>38.2</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>8.6</v>
+        <v>23.9</v>
       </c>
       <c r="V8" t="n">
-        <v>46.8</v>
+        <v>0.22</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>23.8731856378915</v>
       </c>
       <c r="X8" t="n">
-        <v>26.4</v>
+        <v>23.5844721732425</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.197952218430034</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
-        <v>26.4196587726</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>26.0831054612881</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1466,29 +1399,22 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
+        <v>94</v>
+      </c>
+      <c r="AK8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1496,85 +1422,85 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>85.36462278500269</v>
+        <v>72.13777473572139</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>28.0890109547142</v>
       </c>
       <c r="E9" t="n">
-        <v>30.4271978579252</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>45</v>
+        <v>379</v>
       </c>
       <c r="I9" t="n">
-        <v>2040</v>
+        <v>491.8</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>284.9</v>
       </c>
       <c r="K9" t="n">
-        <v>78</v>
+        <v>1155.7</v>
       </c>
       <c r="L9" t="n">
-        <v>26.4</v>
+        <v>140.4</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>193.1</v>
       </c>
       <c r="N9" t="n">
-        <v>104.4</v>
+        <v>44</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>377.5</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>12.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>30.2</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>26.55</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>26.5151515151515</v>
       </c>
       <c r="X9" t="n">
-        <v>22.9</v>
+        <v>26.2096759585991</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.271698113207547</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>23.2365673542144</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>22.6736985933985</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1583,10 +1509,10 @@
         <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
@@ -1595,24 +1521,15 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>96</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>186</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>570</v>
+        <v>633</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1620,40 +1537,40 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>80.10493763784319</v>
+        <v>82.8868868355008</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>37.4213957794838</v>
       </c>
       <c r="E10" t="n">
-        <v>31.2213039485766</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>187</v>
       </c>
       <c r="I10" t="n">
-        <v>1180</v>
+        <v>63.9</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>165.6</v>
       </c>
       <c r="K10" t="n">
-        <v>60</v>
+        <v>416.5</v>
       </c>
       <c r="L10" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>293</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1671,34 +1588,34 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>24.8</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>25.305576776165</v>
       </c>
       <c r="X10" t="n">
-        <v>27.2</v>
+        <v>24.856233988737</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.294670846394984</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>27.6928953399542</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>26.5066584133226</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1707,10 +1624,10 @@
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
@@ -1719,22 +1636,15 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="AK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN10" t="inlineStr"/>
+        <v>236</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>599</v>
+        <v>2397</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1742,85 +1652,85 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>83.724576013385</v>
+        <v>76.83366827642151</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>29.3847566574839</v>
       </c>
       <c r="E11" t="n">
-        <v>28.515625</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>60</v>
+        <v>818.8</v>
       </c>
       <c r="I11" t="n">
-        <v>3870</v>
+        <v>45.1</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>9.9</v>
       </c>
       <c r="K11" t="n">
-        <v>307.1</v>
+        <v>873.8</v>
       </c>
       <c r="L11" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>87.2</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>739.3</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>45.5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>55.9</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>24.3</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>24.5416348357525</v>
       </c>
       <c r="X11" t="n">
-        <v>24.05</v>
+        <v>24.4249070315066</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.113725490196078</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>24.3188184364655</v>
+        <v>1</v>
       </c>
       <c r="AA11" t="n">
-        <v>24.152404368873</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1838,22 +1748,13 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>156</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>188</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
